--- a/Cards/Generation/data/validation/candidate_card_annotations.xlsx
+++ b/Cards/Generation/data/validation/candidate_card_annotations.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annotations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="rubric" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annotations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annotations'!$A$1:$Z$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annotations'!$A$1:$Z$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -921,8 +921,216 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>MINISTRAL3_8B_COE_WE_CAN_1_1_0130</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Ministral 3 8B</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ministral3_8b_candidate_cards.jsonl</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T10:27:10+02:00</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1.1 threats of harm</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Direct or indirect threats of harm, violence, punishment, or intimidation against women or gendered subjects.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>COE_WE_CAN</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>We CAN! Taking action against hate speech through counter and alternative narratives</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Council of Europe</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://rm.coe.int/wecan-eng-final-23052017-web/168071ba08</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>80 and ideas of alternatives to violence. In this manual, several options and emphases are proposed, but ultimately it is up to campaigners to choose the most appropriate approach, message and tone of their campaign. 5.3 | COUNTER MESSAGING: OCCUPYING PUBLIC SPACE3 Counter messages are a short and direct reaction to hateful messages. They are a form of counter narrative, which can be used to directly de-construct, discredit and demys- tify violent extremist messages. They are often used as an instrument to block or to challenge concrete expressions of hate. The following two scenarios are among the most common where such an instrument can be extremely useful: • an outburst of hate targeting a specific minority following specific events (dis- cussion of law protecting a minority, specific historical dates, reactions against crimes allegedly committed by members of this minorities, and so on) which need a quick reaction • a hateful narrative in a position of strength (due to the political landscape, or a well-rooted prejudice in society), which activists and movements want to weak- en, or start to challenge. The main objective of short-term counter narratives is to occupy public spaces, either online, such as producing memes mocking hateful contents, or offline by expressions of “love speech” , including the subversion of hate speech on graffiti walls. Activists, educators and youth workers can at the same time: HOW COULD OLI USE A COUNTER NARRATIVE TO COMBAT HATE SPEECH? Oli thinks that she could discredit the xenophobic narrative underlying the threats she received. She could explain that Rolonians are not a threat to so - ciety. For example, she could invite a famous and popular Rolonian-origin singer to participate in a campaign. She could organise a special seminar at her school presenting historical and current socio-economic facts and differ - ent points of view on the issue of immigration. For example: “Marcadia is a country where many communities have contributed to its prosperity. Among them, Rolonians have lived in the country for more than a century and have created jobs for many Marcadians. With the economic crisis, no Rolonians want to</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>The passage emphasizes that counter-narratives can directly challenge hateful threats by occupying public spaces and providing factual, alternative perspectives. It highlights the effectiveness of short-term interventions—such as organizing educational seminars or featuring public figures—to dismantle harmful narratives rooted in prejudice or misinformation. This approach is particularly useful when hate speech is tied to political narratives or well-entrenched societal biases, as it disrupts the perceived legitimacy of threats by replacing them with evidence-based counterpoints.</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>Threats against Rolonians in Marcadia ignore the long-standing contributions of this community to the country’s economy and social fabric. Over a century of residency includes job creation for Marcadians, and the current economic crisis has not deterred Rolonians from continuing to integrate and thrive. Facts matter more than fear—let’s focus on the shared prosperity we’ve built together.</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>This argument addresses 1.1 threats of harm. EDOS definition: Direct or indirect threats of harm, violence, punishment, or intimidation against women or gendered subjects.</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1.1 threats of harm; threats; harm; against; rolonians; marcadia; ignore; long-standing; contributions; community</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>MINISTRAL3_8B_EPRS_2021_CYBERVIOLENCE_1_1_0370</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ministral 3 8B</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ministral3_8b_candidate_cards.jsonl</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29T10:27:31+02:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1.1 threats of harm</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Direct or indirect threats of harm, violence, punishment, or intimidation against women or gendered subjects.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>EPRS_2021_CYBERVIOLENCE</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Combating gender-based violence: Cyber violence</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>European Parliamentary Research Service / European Parliament</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/RegData/etudes/STUD/2021/662621/EPRS_STU(2021)662621_EN.pdf</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>capable of raising reasonable fear for life or health, an offender can be sentenced to prohibition of activity or up to one yea r imprisonment. Establishment, Support and Promotion of Movements Aimed at Suppression of Human Rights and Freedoms (Section 403) aims to tackle movements that suppress human rights or proclaim hatred against specific groups of people. Although gender is n ot specifically noted, paragraph (1) of th e section includes a general criterion (‘hatred against another group of people’), which could be used in a gender context. The second paragraph recognises the amplification of such hate speech by using publicly accessible computer networks, which brings an aggravated sentence of up to ten year s ’ imprisonment. Incitement to hatred against a group of persons or restriction of their rights and freedoms ( Se ction 356 paragraph 3 a). Although gender is not specifically noted, paragraph (1) of the section includes a general criterion (‘hatred against another group of people’), which could be used in a gender context. A milder form of misconduct may be considered as a misdemeanour (Section 7 – Offenses against civil cohabitation, Act No. 251/2016) Person who considers that his / her personality rights have been violated may claim protection against such interference in civil proceedings, as well as compensation for non-pecuniary damage. A notable case is that of former footballer Tomas Řepka and his partner Kateřina Kristelová. Mr Řepka was found guilty of advertising sexual services on an erotic website in the name of his ex-wife, including her actual phone number. Under Section 181, Mr Řepka was originally sentenced to six m onths’ im prisonment, reduced to 300 hours of community service by the Court of Appeal, for the crime of damage to the rights of another person, and Ms Kristelová was fined CZK 50,000. 341 Although the legal framework covers a range of relevant crimes, a 2016 report by the Council of Europe’s Committee on the Elimination of Discrimination against Women noted a range of concerns in relation to the Czech approach to tackling violence against women, including: i) a lack of gender sensitivity</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>The passage highlights that legal frameworks in some jurisdictions (e.g., Section 403 and Section 356) explicitly criminalize hate speech against groups, including gendered ones, with penalties like imprisonment (up to 10 years for online amplification). This establishes that threats of harm against women or gendered subjects are not only socially unacceptable but also legally actionable, reinforcing the idea that such speech undermines societal norms and legal protections.</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Threats of harm against women or gendered groups are not only harmful in practice but also explicitly prohibited under laws like Section 403 and Section 356, which criminalize hate speech and intimidation with severe penalties. By targeting individuals or groups with violence, you violate legal protections and undermine public safety, as these laws exist precisely to prevent such escalation. Your words carry real consequences, not just for the targeted community but for the broader framework of justice and equality.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>This argument addresses 1.1 threats of harm. EDOS definition: Direct or indirect threats of harm, violence, punishment, or intimidation against women or gendered subjects.</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1.1 threats of harm; threats; harm; against; women; gendered; groups; harmful; practice; explicitly</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z4"/>
+  <autoFilter ref="A1:Z6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
